--- a/salidas/empresas/KLAC.xlsx
+++ b/salidas/empresas/KLAC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>2.746040821075439</v>
+        <v>2.746041774749756</v>
       </c>
       <c r="C2" t="n">
         <v>5.197999954223633</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>2.765514135360718</v>
+        <v>2.765514612197876</v>
       </c>
       <c r="C3" t="n">
         <v>5.223000049591064</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>2.560602426528931</v>
+        <v>2.560604333877563</v>
       </c>
       <c r="C4" t="n">
         <v>4.835999965667725</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>2.550012588500977</v>
+        <v>2.550012111663818</v>
       </c>
       <c r="C5" t="n">
         <v>4.815999984741211</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>2.178433179855347</v>
+        <v>2.178432941436768</v>
       </c>
       <c r="C6" t="n">
         <v>4.104000091552734</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>2.206566095352173</v>
+        <v>2.20656681060791</v>
       </c>
       <c r="C7" t="n">
         <v>4.157000064849854</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>2.23947548866272</v>
+        <v>2.239475727081299</v>
       </c>
       <c r="C8" t="n">
         <v>4.218999862670898</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>2.337538719177246</v>
+        <v>2.337538957595825</v>
       </c>
       <c r="C9" t="n">
         <v>4.390999794006348</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>2.367350816726685</v>
+        <v>2.367349863052368</v>
       </c>
       <c r="C10" t="n">
         <v>4.447000026702881</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>2.617552757263184</v>
+        <v>2.617554426193237</v>
       </c>
       <c r="C11" t="n">
         <v>4.916999816894531</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>2.757456064224243</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="C12" t="n">
         <v>5.166999816894531</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>2.654992341995239</v>
+        <v>2.654991865158081</v>
       </c>
       <c r="C13" t="n">
         <v>4.974999904632568</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>2.767881393432617</v>
+        <v>2.767880916595459</v>
       </c>
       <c r="C15" t="n">
         <v>5.173999786376953</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>2.971701622009277</v>
+        <v>2.971701145172119</v>
       </c>
       <c r="C17" t="n">
         <v>5.554999828338623</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>2.947617530822754</v>
+        <v>2.947618722915649</v>
       </c>
       <c r="C18" t="n">
         <v>5.498000144958496</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>2.946009635925293</v>
+        <v>2.946010828018188</v>
       </c>
       <c r="C19" t="n">
         <v>5.494999885559082</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>3.04465651512146</v>
+        <v>3.044656991958618</v>
       </c>
       <c r="C20" t="n">
         <v>5.678999900817871</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>3.089240789413452</v>
+        <v>3.089241743087769</v>
       </c>
       <c r="C21" t="n">
         <v>5.747000217437744</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>2.59656810760498</v>
+        <v>2.596567153930664</v>
       </c>
       <c r="C25" t="n">
         <v>4.815999984741211</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>2.252587795257568</v>
+        <v>2.25258731842041</v>
       </c>
       <c r="C26" t="n">
         <v>4.177999973297119</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>2.273046970367432</v>
+        <v>2.273047685623169</v>
       </c>
       <c r="C27" t="n">
         <v>4.201000213623047</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>2.007380723953247</v>
+        <v>2.007380485534668</v>
       </c>
       <c r="C28" t="n">
         <v>3.710000038146973</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>2.363406181335449</v>
+        <v>2.363406658172607</v>
       </c>
       <c r="C29" t="n">
         <v>4.368000030517578</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>2.503625154495239</v>
+        <v>2.503625631332397</v>
       </c>
       <c r="C30" t="n">
         <v>4.611999988555908</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>2.209944009780884</v>
+        <v>2.209943056106567</v>
       </c>
       <c r="C31" t="n">
         <v>4.071000099182129</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>2.040574073791504</v>
+        <v>2.040574550628662</v>
       </c>
       <c r="C32" t="n">
         <v>3.759000062942505</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>2.019470691680908</v>
+        <v>2.019470453262329</v>
       </c>
       <c r="C33" t="n">
         <v>3.706000089645386</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>1.724669337272644</v>
+        <v>1.724668979644775</v>
       </c>
       <c r="C34" t="n">
         <v>3.164999961853027</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>1.035181522369385</v>
+        <v>1.035181999206543</v>
       </c>
       <c r="C36" t="n">
         <v>1.88100004196167</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>1.199181079864502</v>
+        <v>1.19918167591095</v>
       </c>
       <c r="C37" t="n">
         <v>2.178999900817871</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>1.102872967720032</v>
+        <v>1.102872848510742</v>
       </c>
       <c r="C38" t="n">
         <v>2.003999948501587</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9573292136192322</v>
+        <v>0.9573290348052979</v>
       </c>
       <c r="C39" t="n">
         <v>1.725000023841858</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>1.109946966171265</v>
+        <v>1.109947323799133</v>
       </c>
       <c r="C40" t="n">
         <v>2</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>1.539496898651123</v>
+        <v>1.539496541023254</v>
       </c>
       <c r="C41" t="n">
         <v>2.773999929428101</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>1.507361769676208</v>
+        <v>1.507361531257629</v>
       </c>
       <c r="C42" t="n">
         <v>2.700000047683716</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>1.409662008285522</v>
+        <v>1.409662365913391</v>
       </c>
       <c r="C43" t="n">
         <v>2.525000095367432</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>1.779803395271301</v>
+        <v>1.77980375289917</v>
       </c>
       <c r="C44" t="n">
         <v>3.187999963760376</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>1.750292658805847</v>
+        <v>1.750293016433716</v>
       </c>
       <c r="C45" t="n">
         <v>3.119999885559082</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>2.011715412139893</v>
+        <v>2.011715650558472</v>
       </c>
       <c r="C46" t="n">
         <v>3.585999965667725</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>1.823782920837402</v>
+        <v>1.823782444000244</v>
       </c>
       <c r="C47" t="n">
         <v>3.250999927520752</v>
@@ -1356,7 +1368,7 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1375,7 +1387,7 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>1.589081048965454</v>
+        <v>1.589081525802612</v>
       </c>
       <c r="C50" t="n">
         <v>2.819999933242798</v>
@@ -1413,7 +1425,7 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>1.751983404159546</v>
+        <v>1.751982808113098</v>
       </c>
       <c r="C52" t="n">
         <v>3.092999935150146</v>
@@ -1451,7 +1463,7 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>1.750825643539429</v>
+        <v>1.750826835632324</v>
       </c>
       <c r="C54" t="n">
         <v>3.07699990272522</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>1.586383461952209</v>
+        <v>1.586383700370789</v>
       </c>
       <c r="C55" t="n">
         <v>2.788000106811523</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>1.802036285400391</v>
+        <v>1.802037000656128</v>
       </c>
       <c r="C56" t="n">
         <v>3.16700005531311</v>
@@ -1527,7 +1539,7 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1546,11 +1558,11 @@
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>2.021572351455688</v>
+        <v>2.021572113037109</v>
       </c>
       <c r="C58" t="n">
         <v>3.523000001907349</v>
@@ -1565,11 +1577,11 @@
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>2.049690246582031</v>
+        <v>2.049689769744873</v>
       </c>
       <c r="C59" t="n">
         <v>3.572000026702881</v>
@@ -1584,11 +1596,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>2.118355751037598</v>
+        <v>2.118355989456177</v>
       </c>
       <c r="C60" t="n">
         <v>3.66700005531311</v>
@@ -1609,7 +1621,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1634,11 +1646,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>2.546415567398071</v>
+        <v>2.546416044235229</v>
       </c>
       <c r="C62" t="n">
         <v>4.407999992370605</v>
@@ -1659,11 +1671,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>2.834754228591919</v>
+        <v>2.834753513336182</v>
       </c>
       <c r="C63" t="n">
         <v>4.881999969482422</v>
@@ -1684,11 +1696,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>2.747654914855957</v>
+        <v>2.74765682220459</v>
       </c>
       <c r="C64" t="n">
         <v>4.73199987411499</v>
@@ -1709,11 +1721,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>2.549072265625</v>
+        <v>2.549072027206421</v>
       </c>
       <c r="C65" t="n">
         <v>4.389999866485596</v>
@@ -1734,11 +1746,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>2.516822814941406</v>
+        <v>2.516823053359985</v>
       </c>
       <c r="C66" t="n">
         <v>4.309999942779541</v>
@@ -1759,11 +1771,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>2.363828182220459</v>
+        <v>2.363826990127563</v>
       </c>
       <c r="C67" t="n">
         <v>4.047999858856201</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>2.325287342071533</v>
+        <v>2.325287103652954</v>
       </c>
       <c r="C68" t="n">
         <v>3.982000112533569</v>
@@ -1809,11 +1821,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>2.16334080696106</v>
+        <v>2.163339614868164</v>
       </c>
       <c r="C69" t="n">
         <v>3.667999982833862</v>
@@ -1838,7 +1850,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1867,11 +1879,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>2.777309656143188</v>
+        <v>2.77730917930603</v>
       </c>
       <c r="C71" t="n">
         <v>4.709000110626221</v>
@@ -1896,11 +1908,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>2.73897123336792</v>
+        <v>2.738970756530762</v>
       </c>
       <c r="C72" t="n">
         <v>4.610000133514404</v>
@@ -1925,11 +1937,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>2.86670994758606</v>
+        <v>2.86670970916748</v>
       </c>
       <c r="C73" t="n">
         <v>4.824999809265137</v>
@@ -1954,11 +1966,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>3.036634922027588</v>
+        <v>3.036633491516113</v>
       </c>
       <c r="C74" t="n">
         <v>5.111000061035156</v>
@@ -1983,7 +1995,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2012,11 +2024,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>3.256397485733032</v>
+        <v>3.256397724151611</v>
       </c>
       <c r="C76" t="n">
         <v>5.441999912261963</v>
@@ -2041,11 +2053,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>3.119367837905884</v>
+        <v>3.119368553161621</v>
       </c>
       <c r="C77" t="n">
         <v>5.212999820709229</v>
@@ -2070,11 +2082,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>2.76170802116394</v>
+        <v>2.761707067489624</v>
       </c>
       <c r="C78" t="n">
         <v>4.583000183105469</v>
@@ -2099,11 +2111,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>2.967796802520752</v>
+        <v>2.967795372009277</v>
       </c>
       <c r="C79" t="n">
         <v>4.925000190734863</v>
@@ -2128,11 +2140,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>3.067828893661499</v>
+        <v>3.06782603263855</v>
       </c>
       <c r="C80" t="n">
         <v>5.091000080108643</v>
@@ -2157,11 +2169,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>3.115484476089478</v>
+        <v>3.115483999252319</v>
       </c>
       <c r="C81" t="n">
         <v>5.13100004196167</v>
@@ -2186,7 +2198,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2215,11 +2227,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>2.826462745666504</v>
+        <v>2.826463460922241</v>
       </c>
       <c r="C83" t="n">
         <v>4.65500020980835</v>
@@ -2244,11 +2256,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>2.785575151443481</v>
+        <v>2.78557562828064</v>
       </c>
       <c r="C84" t="n">
         <v>4.546999931335449</v>
@@ -2273,11 +2285,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>2.925864934921265</v>
+        <v>2.925865888595581</v>
       </c>
       <c r="C85" t="n">
         <v>4.776000022888184</v>
@@ -2302,11 +2314,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>3.363887786865234</v>
+        <v>3.363888025283813</v>
       </c>
       <c r="C86" t="n">
         <v>5.491000175476074</v>
@@ -2331,11 +2343,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>3.378570318222046</v>
+        <v>3.378571748733521</v>
       </c>
       <c r="C87" t="n">
         <v>5.47599983215332</v>
@@ -2360,11 +2372,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>3.253941297531128</v>
+        <v>3.253940105438232</v>
       </c>
       <c r="C88" t="n">
         <v>5.27400016784668</v>
@@ -2389,11 +2401,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>3.347104549407959</v>
+        <v>3.347105264663696</v>
       </c>
       <c r="C89" t="n">
         <v>5.425000190734863</v>
@@ -2418,11 +2430,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>3.498551845550537</v>
+        <v>3.498552083969116</v>
       </c>
       <c r="C90" t="n">
         <v>5.629000186920166</v>
@@ -2447,11 +2459,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>3.463746547698975</v>
+        <v>3.463745594024658</v>
       </c>
       <c r="C91" t="n">
         <v>5.572999954223633</v>
@@ -2476,11 +2488,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>3.643988132476807</v>
+        <v>3.643987655639648</v>
       </c>
       <c r="C92" t="n">
         <v>5.86299991607666</v>
@@ -2505,11 +2517,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>3.453886270523071</v>
+        <v>3.453885316848755</v>
       </c>
       <c r="C93" t="n">
         <v>5.514999866485596</v>
@@ -2534,11 +2546,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>3.81085991859436</v>
+        <v>3.810860633850098</v>
       </c>
       <c r="C94" t="n">
         <v>6.085000038146973</v>
@@ -2563,7 +2575,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2592,11 +2604,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>4.028349876403809</v>
+        <v>4.028348922729492</v>
       </c>
       <c r="C96" t="n">
         <v>6.38700008392334</v>
@@ -2621,11 +2633,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>4.065562725067139</v>
+        <v>4.065560817718506</v>
       </c>
       <c r="C97" t="n">
         <v>6.446000099182129</v>
@@ -2650,11 +2662,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>3.87697958946228</v>
+        <v>3.876979112625122</v>
       </c>
       <c r="C98" t="n">
         <v>6.146999835968018</v>
@@ -2679,11 +2691,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>4.138272762298584</v>
+        <v>4.138274192810059</v>
       </c>
       <c r="C99" t="n">
         <v>6.514999866485596</v>
@@ -2708,11 +2720,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>4.391715049743652</v>
+        <v>4.391714572906494</v>
       </c>
       <c r="C100" t="n">
         <v>6.914000034332275</v>
@@ -2737,11 +2749,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>4.064589977264404</v>
+        <v>4.064591407775879</v>
       </c>
       <c r="C101" t="n">
         <v>6.39900016784668</v>
@@ -2766,7 +2778,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2795,11 +2807,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>4.647232055664062</v>
+        <v>4.647231578826904</v>
       </c>
       <c r="C103" t="n">
         <v>7.263999938964844</v>
@@ -2824,11 +2836,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>4.573659420013428</v>
+        <v>4.573658466339111</v>
       </c>
       <c r="C104" t="n">
         <v>7.14900016784668</v>
@@ -2853,11 +2865,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>4.922811985015869</v>
+        <v>4.922812938690186</v>
       </c>
       <c r="C105" t="n">
         <v>7.642000198364258</v>
@@ -2882,11 +2894,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>5.074838161468506</v>
+        <v>5.074839115142822</v>
       </c>
       <c r="C106" t="n">
         <v>7.877999782562256</v>
@@ -2911,11 +2923,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>5.098673343658447</v>
+        <v>5.098673820495605</v>
       </c>
       <c r="C107" t="n">
         <v>7.914999961853027</v>
@@ -2940,11 +2952,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>5.598822116851807</v>
+        <v>5.59882116317749</v>
       </c>
       <c r="C108" t="n">
         <v>6.943999767303467</v>
@@ -2969,11 +2981,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>5.66977596282959</v>
+        <v>5.669775009155273</v>
       </c>
       <c r="C109" t="n">
         <v>7.032000064849854</v>
@@ -2998,11 +3010,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>4.956215858459473</v>
+        <v>4.956214427947998</v>
       </c>
       <c r="C110" t="n">
         <v>6.146999835968018</v>
@@ -3027,11 +3039,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>5.278874397277832</v>
+        <v>5.278873443603516</v>
       </c>
       <c r="C111" t="n">
         <v>6.495999813079834</v>
@@ -3056,11 +3068,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>4.736847877502441</v>
+        <v>4.736846923828125</v>
       </c>
       <c r="C112" t="n">
         <v>5.828999996185303</v>
@@ -3085,11 +3097,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>4.77829122543335</v>
+        <v>4.778292179107666</v>
       </c>
       <c r="C113" t="n">
         <v>5.880000114440918</v>
@@ -3114,11 +3126,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>4.889701366424561</v>
+        <v>4.889699459075928</v>
       </c>
       <c r="C114" t="n">
         <v>5.966000080108643</v>
@@ -3143,11 +3155,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>4.606940746307373</v>
+        <v>4.606941699981689</v>
       </c>
       <c r="C115" t="n">
         <v>5.620999813079834</v>
@@ -3172,11 +3184,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>4.347949504852295</v>
+        <v>4.347947597503662</v>
       </c>
       <c r="C116" t="n">
         <v>5.304999828338623</v>
@@ -3201,11 +3213,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>4.147468566894531</v>
+        <v>4.147465705871582</v>
       </c>
       <c r="C117" t="n">
         <v>5.011000156402588</v>
@@ -3230,11 +3242,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>4.138360977172852</v>
+        <v>4.138363361358643</v>
       </c>
       <c r="C118" t="n">
         <v>5</v>
@@ -3259,11 +3271,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>5.555336952209473</v>
+        <v>5.555338859558105</v>
       </c>
       <c r="C119" t="n">
         <v>6.711999893188477</v>
@@ -3288,11 +3300,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>5.544635772705078</v>
+        <v>5.544636726379395</v>
       </c>
       <c r="C120" t="n">
         <v>6.646999835968018</v>
@@ -3317,11 +3329,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>5.784873485565186</v>
+        <v>5.784874439239502</v>
       </c>
       <c r="C121" t="n">
         <v>6.934999942779541</v>
@@ -3346,7 +3358,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3375,11 +3387,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>5.69676685333252</v>
+        <v>5.696767807006836</v>
       </c>
       <c r="C123" t="n">
         <v>6.77400016784668</v>
@@ -3404,11 +3416,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>6.123141765594482</v>
+        <v>6.123141288757324</v>
       </c>
       <c r="C124" t="n">
         <v>7.281000137329102</v>
@@ -3433,11 +3445,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>5.881782531738281</v>
+        <v>5.881781578063965</v>
       </c>
       <c r="C125" t="n">
         <v>6.99399995803833</v>
@@ -3462,7 +3474,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3491,11 +3503,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>6.206447124481201</v>
+        <v>6.206446170806885</v>
       </c>
       <c r="C127" t="n">
         <v>7.324999809265137</v>
@@ -3520,7 +3532,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3549,11 +3561,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>5.912632465362549</v>
+        <v>5.912634372711182</v>
       </c>
       <c r="C129" t="n">
         <v>6.926000118255615</v>
@@ -3578,7 +3590,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3607,11 +3619,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>6.412040710449219</v>
+        <v>6.412039756774902</v>
       </c>
       <c r="C131" t="n">
         <v>7.511000156402588</v>
@@ -3636,11 +3648,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>6.864941120147705</v>
+        <v>6.864941596984863</v>
       </c>
       <c r="C132" t="n">
         <v>7.984000205993652</v>
@@ -3665,7 +3677,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3694,11 +3706,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>7.318075656890869</v>
+        <v>7.318074226379395</v>
       </c>
       <c r="C134" t="n">
         <v>8.51099967956543</v>
@@ -3723,11 +3735,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>7.797453880310059</v>
+        <v>7.797452926635742</v>
       </c>
       <c r="C135" t="n">
         <v>9.01200008392334</v>
@@ -3752,11 +3764,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>8.225740432739258</v>
+        <v>8.225743293762207</v>
       </c>
       <c r="C136" t="n">
         <v>9.506999969482422</v>
@@ -3781,11 +3793,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>8.498287200927734</v>
+        <v>8.498290061950684</v>
       </c>
       <c r="C137" t="n">
         <v>9.821999549865723</v>
@@ -3810,11 +3822,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>9.046875953674316</v>
+        <v>9.046873092651367</v>
       </c>
       <c r="C138" t="n">
         <v>10.39999961853027</v>
@@ -3839,11 +3851,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>7.960379600524902</v>
+        <v>7.96038293838501</v>
       </c>
       <c r="C139" t="n">
         <v>9.151000022888184</v>
@@ -3868,11 +3880,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>8.057806015014648</v>
+        <v>8.057811737060547</v>
       </c>
       <c r="C140" t="n">
         <v>9.262999534606934</v>
@@ -3897,11 +3909,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>8.204941749572754</v>
+        <v>8.204943656921387</v>
       </c>
       <c r="C141" t="n">
         <v>9.369000434875488</v>
@@ -3926,11 +3938,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>9.282995223999023</v>
+        <v>9.282994270324707</v>
       </c>
       <c r="C142" t="n">
         <v>10.60000038146973</v>
@@ -3955,11 +3967,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>9.536086082458496</v>
+        <v>9.536087036132812</v>
       </c>
       <c r="C143" t="n">
         <v>10.88899993896484</v>
@@ -3984,7 +3996,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4013,7 +4025,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4042,11 +4054,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>9.671762466430664</v>
+        <v>9.671764373779297</v>
       </c>
       <c r="C146" t="n">
         <v>10.97999954223633</v>
@@ -4071,11 +4083,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>10.03777122497559</v>
+        <v>10.03777503967285</v>
       </c>
       <c r="C147" t="n">
         <v>11.33100032806396</v>
@@ -4100,11 +4112,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>9.656848907470703</v>
+        <v>9.65684986114502</v>
       </c>
       <c r="C148" t="n">
         <v>10.90100002288818</v>
@@ -4129,11 +4141,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>9.012825012207031</v>
+        <v>9.012822151184082</v>
       </c>
       <c r="C149" t="n">
         <v>10.17399978637695</v>
@@ -4158,11 +4170,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>10.09887886047363</v>
+        <v>10.09888076782227</v>
       </c>
       <c r="C150" t="n">
         <v>11.32299995422363</v>
@@ -4187,11 +4199,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>9.14455509185791</v>
+        <v>9.144553184509277</v>
       </c>
       <c r="C151" t="n">
         <v>10.25300025939941</v>
@@ -4216,7 +4228,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4245,11 +4257,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>10.43202209472656</v>
+        <v>10.43202495574951</v>
       </c>
       <c r="C153" t="n">
         <v>11.62100028991699</v>
@@ -4274,11 +4286,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>9.130374908447266</v>
+        <v>9.130377769470215</v>
       </c>
       <c r="C154" t="n">
         <v>10.17099952697754</v>
@@ -4303,11 +4315,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>8.217430114746094</v>
+        <v>8.217429161071777</v>
       </c>
       <c r="C155" t="n">
         <v>9.154000282287598</v>
@@ -4332,11 +4344,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>8.920069694519043</v>
+        <v>8.920071601867676</v>
       </c>
       <c r="C156" t="n">
         <v>9.855999946594238</v>
@@ -4361,7 +4373,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4390,11 +4402,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>9.64500617980957</v>
+        <v>9.645008087158203</v>
       </c>
       <c r="C158" t="n">
         <v>10.6569995880127</v>
@@ -4419,11 +4431,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>10.52547836303711</v>
+        <v>10.52547931671143</v>
       </c>
       <c r="C159" t="n">
         <v>11.54899978637695</v>
@@ -4448,11 +4460,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>10.88273906707764</v>
+        <v>10.882737159729</v>
       </c>
       <c r="C160" t="n">
         <v>11.94099998474121</v>
@@ -4477,11 +4489,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>11.61821937561035</v>
+        <v>11.6182165145874</v>
       </c>
       <c r="C161" t="n">
         <v>12.7480001449585</v>
@@ -4506,11 +4518,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>9.458736419677734</v>
+        <v>9.458735466003418</v>
       </c>
       <c r="C162" t="n">
         <v>10.30700016021729</v>
@@ -4535,11 +4547,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>10.84721279144287</v>
+        <v>10.8472146987915</v>
       </c>
       <c r="C163" t="n">
         <v>11.81999969482422</v>
@@ -4564,11 +4576,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>12.51008796691895</v>
+        <v>12.51008701324463</v>
       </c>
       <c r="C164" t="n">
         <v>13.63199996948242</v>
@@ -4593,11 +4605,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>13.64848613739014</v>
+        <v>13.6484842300415</v>
       </c>
       <c r="C165" t="n">
         <v>14.78999996185303</v>
@@ -4622,11 +4634,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>14.71434116363525</v>
+        <v>14.7143383026123</v>
       </c>
       <c r="C166" t="n">
         <v>15.94499969482422</v>
@@ -4651,11 +4663,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>15.59932231903076</v>
+        <v>15.59932994842529</v>
       </c>
       <c r="C167" t="n">
         <v>16.90399932861328</v>
@@ -4680,11 +4692,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>15.19443893432617</v>
+        <v>15.1944408416748</v>
       </c>
       <c r="C168" t="n">
         <v>16.38599967956543</v>
@@ -4709,11 +4721,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>16.5213794708252</v>
+        <v>16.52137565612793</v>
       </c>
       <c r="C169" t="n">
         <v>17.8169994354248</v>
@@ -4738,11 +4750,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>15.36876392364502</v>
+        <v>15.36876773834229</v>
       </c>
       <c r="C170" t="n">
         <v>16.57399940490723</v>
@@ -4767,11 +4779,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>14.32362937927246</v>
+        <v>14.32363033294678</v>
       </c>
       <c r="C171" t="n">
         <v>15.37100028991699</v>
@@ -4796,11 +4808,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>13.39456748962402</v>
+        <v>13.39456653594971</v>
       </c>
       <c r="C172" t="n">
         <v>14.37399959564209</v>
@@ -4825,11 +4837,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>15.29090595245361</v>
+        <v>15.2909049987793</v>
       </c>
       <c r="C173" t="n">
         <v>16.40900039672852</v>
@@ -4854,11 +4866,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>16.47626113891602</v>
+        <v>16.47625732421875</v>
       </c>
       <c r="C174" t="n">
         <v>17.59600067138672</v>
@@ -4883,11 +4895,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>18.21040153503418</v>
+        <v>18.21040344238281</v>
       </c>
       <c r="C175" t="n">
         <v>19.44799995422363</v>
@@ -4912,11 +4924,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>18.71135330200195</v>
+        <v>18.71135711669922</v>
       </c>
       <c r="C176" t="n">
         <v>19.98299980163574</v>
@@ -4941,11 +4953,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>19.29125785827637</v>
+        <v>19.29125595092773</v>
       </c>
       <c r="C177" t="n">
         <v>20.51399993896484</v>
@@ -4970,7 +4982,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -4999,11 +5011,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>18.54270553588867</v>
+        <v>18.54270362854004</v>
       </c>
       <c r="C179" t="n">
         <v>19.7180004119873</v>
@@ -5028,7 +5040,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5057,11 +5069,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>24.44206809997559</v>
+        <v>24.44206428527832</v>
       </c>
       <c r="C181" t="n">
         <v>25.89100074768066</v>
@@ -5086,11 +5098,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>26.43964385986328</v>
+        <v>26.43964958190918</v>
       </c>
       <c r="C182" t="n">
         <v>28.00699996948242</v>
@@ -5115,11 +5127,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>29.4615478515625</v>
+        <v>29.4615421295166</v>
       </c>
       <c r="C183" t="n">
         <v>31.12299919128418</v>
@@ -5144,11 +5156,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>31.27621269226074</v>
+        <v>31.27620887756348</v>
       </c>
       <c r="C184" t="n">
         <v>33.04000091552734</v>
@@ -5173,11 +5185,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>29.8515510559082</v>
+        <v>29.85154914855957</v>
       </c>
       <c r="C185" t="n">
         <v>31.53499984741211</v>
@@ -5202,11 +5214,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>30.08858108520508</v>
+        <v>30.08857917785645</v>
       </c>
       <c r="C186" t="n">
         <v>31.68899917602539</v>
@@ -5231,11 +5243,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>30.78361701965332</v>
+        <v>30.78361320495605</v>
       </c>
       <c r="C187" t="n">
         <v>32.42100143432617</v>
@@ -5260,7 +5272,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5289,11 +5301,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>32.38257217407227</v>
+        <v>32.38256454467773</v>
       </c>
       <c r="C189" t="n">
         <v>33.99599838256836</v>
@@ -5318,11 +5330,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>31.86343574523926</v>
+        <v>31.86343193054199</v>
       </c>
       <c r="C190" t="n">
         <v>33.45100021362305</v>
@@ -5347,11 +5359,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>35.50690841674805</v>
+        <v>35.50691223144531</v>
       </c>
       <c r="C191" t="n">
         <v>37.2760009765625</v>
@@ -5376,11 +5388,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>38.97517776489258</v>
+        <v>38.97518157958984</v>
       </c>
       <c r="C192" t="n">
         <v>40.8129997253418</v>
@@ -5405,7 +5417,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5434,11 +5446,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>37.17410659790039</v>
+        <v>37.17411041259766</v>
       </c>
       <c r="C194" t="n">
         <v>38.92699813842773</v>
@@ -5463,11 +5475,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>33.3706169128418</v>
+        <v>33.37059783935547</v>
       </c>
       <c r="C195" t="n">
         <v>34.84999847412109</v>
@@ -5492,11 +5504,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>35.05206298828125</v>
+        <v>35.05205535888672</v>
       </c>
       <c r="C196" t="n">
         <v>36.60599899291992</v>
@@ -5521,11 +5533,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>30.57073402404785</v>
+        <v>30.57073211669922</v>
       </c>
       <c r="C197" t="n">
         <v>31.92600059509277</v>
@@ -5550,11 +5562,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>35.05282211303711</v>
+        <v>35.05282592773438</v>
       </c>
       <c r="C198" t="n">
         <v>36.48500061035156</v>
@@ -5579,11 +5591,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>30.65548896789551</v>
+        <v>30.65548706054688</v>
       </c>
       <c r="C199" t="n">
         <v>31.90800094604492</v>
@@ -5608,11 +5620,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>36.84846878051758</v>
+        <v>36.84845733642578</v>
       </c>
       <c r="C200" t="n">
         <v>38.35400009155273</v>
@@ -5637,11 +5649,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>33.17786026000977</v>
+        <v>33.17786407470703</v>
       </c>
       <c r="C201" t="n">
         <v>34.41299819946289</v>
@@ -5666,11 +5678,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>29.17681503295898</v>
+        <v>29.17681312561035</v>
       </c>
       <c r="C202" t="n">
         <v>30.26300048828125</v>
@@ -5695,11 +5707,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>30.50921249389648</v>
+        <v>30.50921440124512</v>
       </c>
       <c r="C203" t="n">
         <v>31.64500045776367</v>
@@ -5724,11 +5736,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>38.03396987915039</v>
+        <v>38.03396606445312</v>
       </c>
       <c r="C204" t="n">
         <v>39.31499862670898</v>
@@ -5753,11 +5765,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>36.47449493408203</v>
+        <v>36.4744987487793</v>
       </c>
       <c r="C205" t="n">
         <v>37.70299911499023</v>
@@ -5782,7 +5794,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5811,11 +5823,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>36.82040023803711</v>
+        <v>36.82039642333984</v>
       </c>
       <c r="C207" t="n">
         <v>37.9379997253418</v>
@@ -5840,7 +5852,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5869,11 +5881,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>37.51529693603516</v>
+        <v>37.51530456542969</v>
       </c>
       <c r="C209" t="n">
         <v>38.65399932861328</v>
@@ -5898,7 +5910,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5927,11 +5939,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>47.2320442199707</v>
+        <v>47.23205184936523</v>
       </c>
       <c r="C211" t="n">
         <v>48.50199890136719</v>
@@ -5956,11 +5968,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>50.04929733276367</v>
+        <v>50.04929351806641</v>
       </c>
       <c r="C212" t="n">
         <v>51.39500045776367</v>
@@ -5985,11 +5997,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>49.00593185424805</v>
+        <v>49.00592803955078</v>
       </c>
       <c r="C213" t="n">
         <v>50.1870002746582</v>
@@ -6014,11 +6026,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>44.78662872314453</v>
+        <v>44.78662109375</v>
       </c>
       <c r="C214" t="n">
         <v>45.86600112915039</v>
@@ -6043,11 +6055,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>45.86464309692383</v>
+        <v>45.86465072631836</v>
       </c>
       <c r="C215" t="n">
         <v>46.97000122070312</v>
@@ -6072,11 +6084,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>53.32670974731445</v>
+        <v>53.32671356201172</v>
       </c>
       <c r="C216" t="n">
         <v>54.46200180053711</v>
@@ -6101,7 +6113,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6130,11 +6142,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>58.16568756103516</v>
+        <v>58.16567993164062</v>
       </c>
       <c r="C218" t="n">
         <v>59.40399932861328</v>
@@ -6159,7 +6171,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6188,11 +6200,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>68.55282592773438</v>
+        <v>68.55281066894531</v>
       </c>
       <c r="C220" t="n">
         <v>69.85700225830078</v>
@@ -6217,7 +6229,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6246,11 +6258,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>74.6866455078125</v>
+        <v>74.68665313720703</v>
       </c>
       <c r="C222" t="n">
         <v>75.9530029296875</v>
@@ -6275,7 +6287,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6304,11 +6316,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>80.9346923828125</v>
+        <v>80.93470001220703</v>
       </c>
       <c r="C224" t="n">
         <v>82.30699920654297</v>
@@ -6333,11 +6345,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>80.72421264648438</v>
+        <v>80.72422027587891</v>
       </c>
       <c r="C225" t="n">
         <v>81.94300079345703</v>
@@ -6362,11 +6374,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>76.2891845703125</v>
+        <v>76.28917694091797</v>
       </c>
       <c r="C226" t="n">
         <v>77.44100189208984</v>
@@ -6391,7 +6403,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6420,11 +6432,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>63.91747665405273</v>
+        <v>63.9174690246582</v>
       </c>
       <c r="C228" t="n">
         <v>64.7030029296875</v>
@@ -6449,7 +6461,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6478,11 +6490,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>72.927734375</v>
+        <v>72.92774200439453</v>
       </c>
       <c r="C230" t="n">
         <v>73.82399749755859</v>
@@ -6507,7 +6519,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6536,7 +6548,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6565,7 +6577,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6594,11 +6606,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>75.11840057373047</v>
+        <v>75.11841583251953</v>
       </c>
       <c r="C234" t="n">
         <v>75.68800354003906</v>
@@ -6623,7 +6635,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6652,7 +6664,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6681,11 +6693,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>86.73210906982422</v>
+        <v>86.73211669921875</v>
       </c>
       <c r="C237" t="n">
         <v>87.19999694824219</v>
@@ -6710,11 +6722,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>107.2812576293945</v>
+        <v>107.2812652587891</v>
       </c>
       <c r="C238" t="n">
         <v>107.8600006103516</v>
@@ -6739,11 +6751,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>120.2254257202148</v>
+        <v>120.2254333496094</v>
       </c>
       <c r="C239" t="n">
         <v>120.8740005493164</v>
@@ -6768,11 +6780,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>117.1124496459961</v>
+        <v>117.1124420166016</v>
       </c>
       <c r="C240" t="n">
         <v>117.5469970703125</v>
@@ -6797,7 +6809,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6826,11 +6838,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>142.2661285400391</v>
+        <v>142.26611328125</v>
       </c>
       <c r="C242" t="n">
         <v>142.7940063476562</v>
@@ -6855,7 +6867,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6884,7 +6896,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6913,11 +6925,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>174.6145172119141</v>
+        <v>174.6145324707031</v>
       </c>
       <c r="C245" t="n">
         <v>175.0350036621094</v>
@@ -6942,7 +6954,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6971,7 +6983,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7000,7 +7012,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7029,7 +7041,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7058,32 +7070,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>187.8600006103516</v>
+        <v>187.1100006103516</v>
       </c>
       <c r="C250" t="n">
-        <v>187.8600006103516</v>
+        <v>187.1100006103516</v>
       </c>
       <c r="D250" t="n">
-        <v>160597000</v>
+        <v>168380600</v>
       </c>
       <c r="E250" t="n">
         <v>3.66</v>
       </c>
       <c r="F250" t="n">
-        <v>51.32786901922174</v>
+        <v>51.12295098643485</v>
       </c>
       <c r="G250" t="n">
         <v>1306546783</v>
       </c>
       <c r="H250" t="n">
-        <v>245447879451.8329</v>
+        <v>244467969364.5829</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1229171447127584</v>
+        <v>0.1288745280236934</v>
       </c>
     </row>
   </sheetData>
@@ -7115,75 +7127,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7219,13 +7231,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7261,13 +7273,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7303,13 +7315,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7336,7 +7348,7 @@
       <c r="I5" t="n">
         <v>0.124</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K5" t="n">
@@ -7349,13 +7361,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7382,7 +7394,7 @@
       <c r="I6" t="n">
         <v>0.203</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K6" t="n">
@@ -7395,13 +7407,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7428,7 +7440,7 @@
       <c r="I7" t="n">
         <v>0.299</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K7" t="n">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7474,7 +7486,7 @@
       <c r="I8" t="n">
         <v>0.388</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K8" t="n">
@@ -7487,13 +7499,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7520,7 +7532,7 @@
       <c r="I9" t="n">
         <v>0.465</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K9" t="n">
@@ -7533,13 +7545,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7566,7 +7578,7 @@
       <c r="I10" t="n">
         <v>0.487</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="K10" t="n">
@@ -7579,13 +7591,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7612,7 +7624,7 @@
       <c r="I11" t="n">
         <v>0.444</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="K11" t="n">
@@ -7625,13 +7637,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7658,7 +7670,7 @@
       <c r="I12" t="n">
         <v>0.4429999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="K12" t="n">
@@ -7671,13 +7683,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7704,7 +7716,7 @@
       <c r="I13" t="n">
         <v>0.446</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="K13" t="n">
@@ -7717,13 +7729,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7750,7 +7762,7 @@
       <c r="I14" t="n">
         <v>0.413</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="K14" t="n">
@@ -7763,13 +7775,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41299</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7796,7 +7808,7 @@
       <c r="I15" t="n">
         <v>0.41</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41299</v>
       </c>
       <c r="K15" t="n">
@@ -7809,13 +7821,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7842,7 +7854,7 @@
       <c r="I16" t="n">
         <v>0.387</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="K16" t="n">
@@ -7855,13 +7867,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7888,7 +7900,7 @@
       <c r="I17" t="n">
         <v>0.321</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K17" t="n">
@@ -7901,13 +7913,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7934,7 +7946,7 @@
       <c r="I18" t="n">
         <v>0.307</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="K18" t="n">
@@ -7947,13 +7959,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41663</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7980,7 +7992,7 @@
       <c r="I19" t="n">
         <v>0.327</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41663</v>
       </c>
       <c r="K19" t="n">
@@ -7993,13 +8005,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8026,7 +8038,7 @@
       <c r="I20" t="n">
         <v>0.35</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="K20" t="n">
@@ -8039,13 +8051,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8072,7 +8084,7 @@
       <c r="I21" t="n">
         <v>0.347</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="K21" t="n">
@@ -8085,13 +8097,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8118,7 +8130,7 @@
       <c r="I22" t="n">
         <v>0.324</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="K22" t="n">
@@ -8131,13 +8143,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42027</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8164,7 +8176,7 @@
       <c r="I23" t="n">
         <v>0.253</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42027</v>
       </c>
       <c r="K23" t="n">
@@ -8177,13 +8189,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8210,7 +8222,7 @@
       <c r="I24" t="n">
         <v>0.213</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="K24" t="n">
@@ -8223,13 +8235,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8256,7 +8268,7 @@
       <c r="I25" t="n">
         <v>0.225</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="K25" t="n">
@@ -8269,13 +8281,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8302,7 +8314,7 @@
       <c r="I26" t="n">
         <v>0.248</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="K26" t="n">
@@ -8315,13 +8327,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42397</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8348,7 +8360,7 @@
       <c r="I27" t="n">
         <v>0.334</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42397</v>
       </c>
       <c r="K27" t="n">
@@ -8361,13 +8373,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8394,7 +8406,7 @@
       <c r="I28" t="n">
         <v>0.365</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="K28" t="n">
@@ -8407,13 +8419,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8440,7 +8452,7 @@
       <c r="I29" t="n">
         <v>0.449</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K29" t="n">
@@ -8453,13 +8465,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8486,7 +8498,7 @@
       <c r="I30" t="n">
         <v>0.496</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="K30" t="n">
@@ -8499,13 +8511,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42762</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8532,7 +8544,7 @@
       <c r="I31" t="n">
         <v>0.55</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42762</v>
       </c>
       <c r="K31" t="n">
@@ -8545,13 +8557,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8578,7 +8590,7 @@
       <c r="I32" t="n">
         <v>0.599</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="K32" t="n">
@@ -8591,13 +8603,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8624,7 +8636,7 @@
       <c r="I33" t="n">
         <v>0.588</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K33" t="n">
@@ -8637,13 +8649,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8670,7 +8682,7 @@
       <c r="I34" t="n">
         <v>0.653</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K34" t="n">
@@ -8683,13 +8695,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43126</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8716,7 +8728,7 @@
       <c r="I35" t="n">
         <v>0.415</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43126</v>
       </c>
       <c r="K35" t="n">
@@ -8729,13 +8741,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8762,7 +8774,7 @@
       <c r="I36" t="n">
         <v>0.449</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K36" t="n">
@@ -8775,13 +8787,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8808,7 +8820,7 @@
       <c r="I37" t="n">
         <v>0.5090000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K37" t="n">
@@ -8821,13 +8833,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8854,7 +8866,7 @@
       <c r="I38" t="n">
         <v>0.585</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="K38" t="n">
@@ -8867,13 +8879,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43494</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8900,7 +8912,7 @@
       <c r="I39" t="n">
         <v>0.913</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43494</v>
       </c>
       <c r="K39" t="n">
@@ -8913,13 +8925,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8946,7 +8958,7 @@
       <c r="I40" t="n">
         <v>0.841</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="K40" t="n">
@@ -8959,13 +8971,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43693</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8992,7 +9004,7 @@
       <c r="I41" t="n">
         <v>0.754</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43693</v>
       </c>
       <c r="K41" t="n">
@@ -9005,13 +9017,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9038,7 +9050,7 @@
       <c r="I42" t="n">
         <v>0.716</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K42" t="n">
@@ -9051,13 +9063,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9084,7 +9096,7 @@
       <c r="I43" t="n">
         <v>0.714</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="K43" t="n">
@@ -9097,13 +9109,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9130,7 +9142,7 @@
       <c r="I44" t="n">
         <v>0.641</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K44" t="n">
@@ -9143,13 +9155,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44053</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9176,7 +9188,7 @@
       <c r="I45" t="n">
         <v>0.769</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44053</v>
       </c>
       <c r="K45" t="n">
@@ -9189,13 +9201,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9222,7 +9234,7 @@
       <c r="I46" t="n">
         <v>0.822</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K46" t="n">
@@ -9235,13 +9247,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9268,7 +9280,7 @@
       <c r="I47" t="n">
         <v>0.8760000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="K47" t="n">
@@ -9281,13 +9293,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9314,7 +9326,7 @@
       <c r="I48" t="n">
         <v>1.192</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K48" t="n">
@@ -9327,13 +9339,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9360,7 +9372,7 @@
       <c r="I49" t="n">
         <v>1.339</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K49" t="n">
@@ -9373,13 +9385,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9406,7 +9418,7 @@
       <c r="I50" t="n">
         <v>1.766</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K50" t="n">
@@ -9419,13 +9431,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9452,7 +9464,7 @@
       <c r="I51" t="n">
         <v>1.943</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="K51" t="n">
@@ -9465,13 +9477,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9498,7 +9510,7 @@
       <c r="I52" t="n">
         <v>2.06</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K52" t="n">
@@ -9511,13 +9523,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9544,7 +9556,7 @@
       <c r="I53" t="n">
         <v>2.192</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K53" t="n">
@@ -9557,13 +9569,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9590,7 +9602,7 @@
       <c r="I54" t="n">
         <v>2.216</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K54" t="n">
@@ -9603,13 +9615,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9636,7 +9648,7 @@
       <c r="I55" t="n">
         <v>2.434</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="K55" t="n">
@@ -9649,13 +9661,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9682,7 +9694,7 @@
       <c r="I56" t="n">
         <v>2.454</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="K56" t="n">
@@ -9695,13 +9707,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9728,7 +9740,7 @@
       <c r="I57" t="n">
         <v>2.415</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K57" t="n">
@@ -9741,13 +9753,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9774,7 +9786,7 @@
       <c r="I58" t="n">
         <v>2.236</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K58" t="n">
@@ -9787,13 +9799,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9820,7 +9832,7 @@
       <c r="I59" t="n">
         <v>1.975</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="K59" t="n">
@@ -9833,13 +9845,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9866,7 +9878,7 @@
       <c r="I60" t="n">
         <v>1.915</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K60" t="n">
@@ -9879,13 +9891,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9912,7 +9924,7 @@
       <c r="I61" t="n">
         <v>2.028</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="K61" t="n">
@@ -9925,13 +9937,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9958,7 +9970,7 @@
       <c r="I62" t="n">
         <v>2.188</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K62" t="n">
@@ -9971,13 +9983,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10004,7 +10016,7 @@
       <c r="I63" t="n">
         <v>2.376</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="K63" t="n">
@@ -10017,13 +10029,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10050,7 +10062,7 @@
       <c r="I64" t="n">
         <v>2.749</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K64" t="n">
@@ -10063,13 +10075,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10096,7 +10108,7 @@
       <c r="I65" t="n">
         <v>3.037</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="K65" t="n">
@@ -10109,13 +10121,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10142,7 +10154,7 @@
       <c r="I66" t="n">
         <v>3.183</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K66" t="n">
@@ -10155,13 +10167,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10188,7 +10200,7 @@
       <c r="I67" t="n">
         <v>3.435</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K67" t="n">
@@ -10201,13 +10213,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10234,7 +10246,7 @@
       <c r="I68" t="n">
         <v>3.531</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K68" t="n">
@@ -10247,13 +10259,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10280,7 +10292,7 @@
       <c r="I69" t="n">
         <v>3.66</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K69" t="n">
@@ -10317,52 +10329,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40464</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="C2" t="n">
@@ -10391,10 +10403,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40556</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40571</v>
       </c>
       <c r="C3" t="n">
@@ -10423,10 +10435,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40647</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="C4" t="n">
@@ -10455,10 +10467,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40745</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C5" t="n">
@@ -10487,10 +10499,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40829</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="C6" t="n">
@@ -10519,10 +10531,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40920</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="C7" t="n">
@@ -10551,10 +10563,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41011</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="C8" t="n">
@@ -10583,10 +10595,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41109</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="C9" t="n">
@@ -10615,10 +10627,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41193</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="C10" t="n">
@@ -10647,10 +10659,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41284</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41299</v>
       </c>
       <c r="C11" t="n">
@@ -10679,10 +10691,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41376</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="C12" t="n">
@@ -10711,10 +10723,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41473</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C13" t="n">
@@ -10743,10 +10755,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41558</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="C14" t="n">
@@ -10775,10 +10787,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41649</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41663</v>
       </c>
       <c r="C15" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41740</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="C16" t="n">
@@ -10839,10 +10851,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41837</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="C17" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41922</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="C18" t="n">
@@ -10903,10 +10915,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42013</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42027</v>
       </c>
       <c r="C19" t="n">
@@ -10935,10 +10947,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42104</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="C20" t="n">
@@ -10967,10 +10979,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42202</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C21" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42286</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="C22" t="n">
@@ -11031,10 +11043,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42384</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42397</v>
       </c>
       <c r="C23" t="n">
@@ -11063,10 +11075,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42475</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="C24" t="n">
@@ -11095,10 +11107,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42566</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C25" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42653</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="C26" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42752</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42762</v>
       </c>
       <c r="C27" t="n">
@@ -11191,10 +11203,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42839</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="C28" t="n">
@@ -11223,10 +11235,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42930</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C29" t="n">
@@ -11255,10 +11267,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43021</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C30" t="n">
@@ -11287,10 +11299,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43112</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43126</v>
       </c>
       <c r="C31" t="n">
@@ -11319,10 +11331,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43203</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C32" t="n">
@@ -11351,10 +11363,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43294</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="C33" t="n">
@@ -11383,10 +11395,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43392</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="C34" t="n">
@@ -11415,10 +11427,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43483</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43494</v>
       </c>
       <c r="C35" t="n">
@@ -11447,10 +11459,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43574</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="C36" t="n">
@@ -11479,10 +11491,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43665</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43693</v>
       </c>
       <c r="C37" t="n">
@@ -11511,10 +11523,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43756</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C38" t="n">
@@ -11543,10 +11555,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43847</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="C39" t="n">
@@ -11575,10 +11587,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43941</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C40" t="n">
@@ -11607,10 +11619,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44032</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44053</v>
       </c>
       <c r="C41" t="n">
@@ -11639,10 +11651,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44123</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C42" t="n">
@@ -11671,10 +11683,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44211</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="C43" t="n">
@@ -11703,10 +11715,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44305</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C44" t="n">
@@ -11735,10 +11747,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44396</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C45" t="n">
@@ -11767,10 +11779,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44487</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C46" t="n">
@@ -11799,10 +11811,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44575</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="C47" t="n">
@@ -11831,10 +11843,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44669</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C48" t="n">
@@ -11863,10 +11875,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44760</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C49" t="n">
@@ -11895,10 +11907,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44851</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C50" t="n">
@@ -11927,10 +11939,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44943</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="C51" t="n">
@@ -11959,10 +11971,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45033</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C52" t="n">
@@ -11991,10 +12003,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C53" t="n">
@@ -12023,10 +12035,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C54" t="n">
@@ -12055,10 +12067,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45307</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="C55" t="n">
@@ -12087,10 +12099,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45397</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C56" t="n">
@@ -12119,10 +12131,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45495</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="C57" t="n">
@@ -12151,10 +12163,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45586</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C58" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45678</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="C59" t="n">
@@ -12215,10 +12227,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45768</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C60" t="n">
@@ -12247,10 +12259,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45859</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="C61" t="n">
@@ -12279,10 +12291,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45957</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C62" t="n">
@@ -12311,10 +12323,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46048</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="C63" t="n">
@@ -12343,10 +12355,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C64" t="n">
@@ -12375,10 +12387,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46237</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C65" t="n">
@@ -12425,12 +12437,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/KLAC.xlsx
+++ b/salidas/empresas/KLAC.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>2.746041774749756</v>
+        <v>2.746042013168335</v>
       </c>
       <c r="C2" t="n">
         <v>5.197999954223633</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>2.765514612197876</v>
+        <v>2.765512943267822</v>
       </c>
       <c r="C3" t="n">
         <v>5.223000049591064</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>2.560604333877563</v>
+        <v>2.560602426528931</v>
       </c>
       <c r="C4" t="n">
         <v>4.835999965667725</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>2.550012111663818</v>
+        <v>2.550012588500977</v>
       </c>
       <c r="C5" t="n">
         <v>4.815999984741211</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>2.20656681060791</v>
+        <v>2.206565380096436</v>
       </c>
       <c r="C7" t="n">
         <v>4.157000064849854</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>2.239475727081299</v>
+        <v>2.23947548866272</v>
       </c>
       <c r="C8" t="n">
         <v>4.218999862670898</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>2.367349863052368</v>
+        <v>2.367351770401001</v>
       </c>
       <c r="C10" t="n">
         <v>4.447000026702881</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>2.617554426193237</v>
+        <v>2.617554187774658</v>
       </c>
       <c r="C11" t="n">
         <v>4.916999816894531</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>2.75745701789856</v>
+        <v>2.757456302642822</v>
       </c>
       <c r="C12" t="n">
         <v>5.166999816894531</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>2.654991865158081</v>
+        <v>2.654991626739502</v>
       </c>
       <c r="C13" t="n">
         <v>4.974999904632568</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>2.628309011459351</v>
+        <v>2.628309488296509</v>
       </c>
       <c r="C14" t="n">
         <v>4.925000190734863</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>2.767880916595459</v>
+        <v>2.767881155014038</v>
       </c>
       <c r="C15" t="n">
         <v>5.173999786376953</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>2.947618722915649</v>
+        <v>2.947619915008545</v>
       </c>
       <c r="C18" t="n">
         <v>5.498000144958496</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>2.946010828018188</v>
+        <v>2.946010589599609</v>
       </c>
       <c r="C19" t="n">
         <v>5.494999885559082</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>3.044656991958618</v>
+        <v>3.044657707214355</v>
       </c>
       <c r="C20" t="n">
         <v>5.678999900817871</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>3.089241743087769</v>
+        <v>3.089239597320557</v>
       </c>
       <c r="C21" t="n">
         <v>5.747000217437744</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>2.998395681381226</v>
+        <v>2.998396158218384</v>
       </c>
       <c r="C22" t="n">
         <v>5.578000068664551</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>2.592253923416138</v>
+        <v>2.592255353927612</v>
       </c>
       <c r="C24" t="n">
         <v>4.808000087738037</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>2.596567153930664</v>
+        <v>2.59656834602356</v>
       </c>
       <c r="C25" t="n">
         <v>4.815999984741211</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>2.25258731842041</v>
+        <v>2.252588033676147</v>
       </c>
       <c r="C26" t="n">
         <v>4.177999973297119</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>2.273047685623169</v>
+        <v>2.273047208786011</v>
       </c>
       <c r="C27" t="n">
         <v>4.201000213623047</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>2.007380485534668</v>
+        <v>2.007379770278931</v>
       </c>
       <c r="C28" t="n">
         <v>3.710000038146973</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>2.363406658172607</v>
+        <v>2.363406419754028</v>
       </c>
       <c r="C29" t="n">
         <v>4.368000030517578</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>2.503625631332397</v>
+        <v>2.503626108169556</v>
       </c>
       <c r="C30" t="n">
         <v>4.611999988555908</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>2.209943056106567</v>
+        <v>2.209944009780884</v>
       </c>
       <c r="C31" t="n">
         <v>4.071000099182129</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>2.040574550628662</v>
+        <v>2.040574312210083</v>
       </c>
       <c r="C32" t="n">
         <v>3.759000062942505</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>2.019470453262329</v>
+        <v>2.019470691680908</v>
       </c>
       <c r="C33" t="n">
         <v>3.706000089645386</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>1.724668979644775</v>
+        <v>1.724668622016907</v>
       </c>
       <c r="C34" t="n">
         <v>3.164999961853027</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>1.266937136650085</v>
+        <v>1.266936898231506</v>
       </c>
       <c r="C35" t="n">
         <v>2.325000047683716</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>1.035181999206543</v>
+        <v>1.035181522369385</v>
       </c>
       <c r="C36" t="n">
         <v>1.88100004196167</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>1.102872848510742</v>
+        <v>1.102873206138611</v>
       </c>
       <c r="C38" t="n">
         <v>2.003999948501587</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9573290348052979</v>
+        <v>0.9573292136192322</v>
       </c>
       <c r="C39" t="n">
         <v>1.725000023841858</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>1.109947323799133</v>
+        <v>1.109946846961975</v>
       </c>
       <c r="C40" t="n">
         <v>2</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>1.539496541023254</v>
+        <v>1.539496302604675</v>
       </c>
       <c r="C41" t="n">
         <v>2.773999929428101</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>1.507361531257629</v>
+        <v>1.507361888885498</v>
       </c>
       <c r="C42" t="n">
         <v>2.700000047683716</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>1.409662365913391</v>
+        <v>1.409662961959839</v>
       </c>
       <c r="C43" t="n">
         <v>2.525000095367432</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>1.77980375289917</v>
+        <v>1.779803514480591</v>
       </c>
       <c r="C44" t="n">
         <v>3.187999963760376</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>1.750293016433716</v>
+        <v>1.750292658805847</v>
       </c>
       <c r="C45" t="n">
         <v>3.119999885559082</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>2.011715650558472</v>
+        <v>2.011714696884155</v>
       </c>
       <c r="C46" t="n">
         <v>3.585999965667725</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>1.823782444000244</v>
+        <v>1.823783040046692</v>
       </c>
       <c r="C47" t="n">
         <v>3.250999927520752</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>1.76038646697998</v>
+        <v>1.76038658618927</v>
       </c>
       <c r="C48" t="n">
         <v>3.124000072479248</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>1.589081525802612</v>
+        <v>1.589081645011902</v>
       </c>
       <c r="C50" t="n">
         <v>2.819999933242798</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>1.650025010108948</v>
+        <v>1.650024890899658</v>
       </c>
       <c r="C51" t="n">
         <v>2.913000106811523</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>1.751982808113098</v>
+        <v>1.751983046531677</v>
       </c>
       <c r="C52" t="n">
         <v>3.092999935150146</v>
@@ -1467,7 +1467,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>1.929276823997498</v>
+        <v>1.92927622795105</v>
       </c>
       <c r="C53" t="n">
         <v>3.405999898910522</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>1.750826835632324</v>
+        <v>1.75082540512085</v>
       </c>
       <c r="C54" t="n">
         <v>3.07699990272522</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>1.586383700370789</v>
+        <v>1.586383581161499</v>
       </c>
       <c r="C55" t="n">
         <v>2.788000106811523</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>1.802037000656128</v>
+        <v>1.802036285400391</v>
       </c>
       <c r="C56" t="n">
         <v>3.16700005531311</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>1.607273578643799</v>
+        <v>1.607273936271667</v>
       </c>
       <c r="C57" t="n">
         <v>2.801000118255615</v>
@@ -1562,7 +1562,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>2.021572113037109</v>
+        <v>2.02157187461853</v>
       </c>
       <c r="C58" t="n">
         <v>3.523000001907349</v>
@@ -1581,7 +1581,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>2.049689769744873</v>
+        <v>2.049690008163452</v>
       </c>
       <c r="C59" t="n">
         <v>3.572000026702881</v>
@@ -1600,7 +1600,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>2.118355989456177</v>
+        <v>2.118355274200439</v>
       </c>
       <c r="C60" t="n">
         <v>3.66700005531311</v>
@@ -1625,7 +1625,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>2.232158660888672</v>
+        <v>2.232158184051514</v>
       </c>
       <c r="C61" t="n">
         <v>3.864000082015991</v>
@@ -1650,7 +1650,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>2.546416044235229</v>
+        <v>2.546416997909546</v>
       </c>
       <c r="C62" t="n">
         <v>4.407999992370605</v>
@@ -1675,7 +1675,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>2.834753513336182</v>
+        <v>2.834753274917603</v>
       </c>
       <c r="C63" t="n">
         <v>4.881999969482422</v>
@@ -1700,7 +1700,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>2.74765682220459</v>
+        <v>2.747656583786011</v>
       </c>
       <c r="C64" t="n">
         <v>4.73199987411499</v>
@@ -1725,7 +1725,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>2.549072027206421</v>
+        <v>2.549071311950684</v>
       </c>
       <c r="C65" t="n">
         <v>4.389999866485596</v>
@@ -1750,7 +1750,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>2.516823053359985</v>
+        <v>2.51682186126709</v>
       </c>
       <c r="C66" t="n">
         <v>4.309999942779541</v>
@@ -1775,7 +1775,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>2.363826990127563</v>
+        <v>2.363828659057617</v>
       </c>
       <c r="C67" t="n">
         <v>4.047999858856201</v>
@@ -1800,7 +1800,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>2.325287103652954</v>
+        <v>2.325287580490112</v>
       </c>
       <c r="C68" t="n">
         <v>3.982000112533569</v>
@@ -1825,7 +1825,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>2.163339614868164</v>
+        <v>2.16334056854248</v>
       </c>
       <c r="C69" t="n">
         <v>3.667999982833862</v>
@@ -1883,7 +1883,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>2.77730917930603</v>
+        <v>2.777308225631714</v>
       </c>
       <c r="C71" t="n">
         <v>4.709000110626221</v>
@@ -1941,7 +1941,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>2.86670970916748</v>
+        <v>2.866711139678955</v>
       </c>
       <c r="C73" t="n">
         <v>4.824999809265137</v>
@@ -1999,7 +1999,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>2.895573139190674</v>
+        <v>2.89557409286499</v>
       </c>
       <c r="C75" t="n">
         <v>4.839000225067139</v>
@@ -2028,7 +2028,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>3.256397724151611</v>
+        <v>3.25639796257019</v>
       </c>
       <c r="C76" t="n">
         <v>5.441999912261963</v>
@@ -2057,7 +2057,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>3.119368553161621</v>
+        <v>3.119368314743042</v>
       </c>
       <c r="C77" t="n">
         <v>5.212999820709229</v>
@@ -2086,7 +2086,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>2.761707067489624</v>
+        <v>2.761706829071045</v>
       </c>
       <c r="C78" t="n">
         <v>4.583000183105469</v>
@@ -2144,7 +2144,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>3.06782603263855</v>
+        <v>3.067827701568604</v>
       </c>
       <c r="C80" t="n">
         <v>5.091000080108643</v>
@@ -2173,7 +2173,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>3.115483999252319</v>
+        <v>3.115485906600952</v>
       </c>
       <c r="C81" t="n">
         <v>5.13100004196167</v>
@@ -2202,7 +2202,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>2.896896600723267</v>
+        <v>2.896897077560425</v>
       </c>
       <c r="C82" t="n">
         <v>4.770999908447266</v>
@@ -2289,7 +2289,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>2.925865888595581</v>
+        <v>2.925865650177002</v>
       </c>
       <c r="C85" t="n">
         <v>4.776000022888184</v>
@@ -2318,7 +2318,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>3.363888025283813</v>
+        <v>3.363887310028076</v>
       </c>
       <c r="C86" t="n">
         <v>5.491000175476074</v>
@@ -2347,7 +2347,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>3.378571748733521</v>
+        <v>3.378570795059204</v>
       </c>
       <c r="C87" t="n">
         <v>5.47599983215332</v>
@@ -2376,7 +2376,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>3.253940105438232</v>
+        <v>3.253939867019653</v>
       </c>
       <c r="C88" t="n">
         <v>5.27400016784668</v>
@@ -2434,7 +2434,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>3.498552083969116</v>
+        <v>3.498551607131958</v>
       </c>
       <c r="C90" t="n">
         <v>5.629000186920166</v>
@@ -2463,7 +2463,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>3.463745594024658</v>
+        <v>3.463745832443237</v>
       </c>
       <c r="C91" t="n">
         <v>5.572999954223633</v>
@@ -2492,7 +2492,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>3.643987655639648</v>
+        <v>3.643988370895386</v>
       </c>
       <c r="C92" t="n">
         <v>5.86299991607666</v>
@@ -2550,7 +2550,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>3.810860633850098</v>
+        <v>3.810861587524414</v>
       </c>
       <c r="C94" t="n">
         <v>6.085000038146973</v>
@@ -2579,7 +2579,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>4.108340263366699</v>
+        <v>4.108338356018066</v>
       </c>
       <c r="C95" t="n">
         <v>6.559999942779541</v>
@@ -2608,7 +2608,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>4.028348922729492</v>
+        <v>4.028349876403809</v>
       </c>
       <c r="C96" t="n">
         <v>6.38700008392334</v>
@@ -2637,7 +2637,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>4.065560817718506</v>
+        <v>4.065561771392822</v>
       </c>
       <c r="C97" t="n">
         <v>6.446000099182129</v>
@@ -2666,7 +2666,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>3.876979112625122</v>
+        <v>3.87697958946228</v>
       </c>
       <c r="C98" t="n">
         <v>6.146999835968018</v>
@@ -2695,7 +2695,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>4.138274192810059</v>
+        <v>4.138273239135742</v>
       </c>
       <c r="C99" t="n">
         <v>6.514999866485596</v>
@@ -2724,7 +2724,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>4.391714572906494</v>
+        <v>4.391715049743652</v>
       </c>
       <c r="C100" t="n">
         <v>6.914000034332275</v>
@@ -2753,7 +2753,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>4.064591407775879</v>
+        <v>4.064591884613037</v>
       </c>
       <c r="C101" t="n">
         <v>6.39900016784668</v>
@@ -2782,7 +2782,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>4.191721439361572</v>
+        <v>4.191720485687256</v>
       </c>
       <c r="C102" t="n">
         <v>6.552000045776367</v>
@@ -2811,7 +2811,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>4.647231578826904</v>
+        <v>4.647232532501221</v>
       </c>
       <c r="C103" t="n">
         <v>7.263999938964844</v>
@@ -2840,7 +2840,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>4.573658466339111</v>
+        <v>4.573659896850586</v>
       </c>
       <c r="C104" t="n">
         <v>7.14900016784668</v>
@@ -2869,7 +2869,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>4.922812938690186</v>
+        <v>4.922810554504395</v>
       </c>
       <c r="C105" t="n">
         <v>7.642000198364258</v>
@@ -2898,7 +2898,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>5.074839115142822</v>
+        <v>5.07483959197998</v>
       </c>
       <c r="C106" t="n">
         <v>7.877999782562256</v>
@@ -2927,7 +2927,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>5.098673820495605</v>
+        <v>5.098672389984131</v>
       </c>
       <c r="C107" t="n">
         <v>7.914999961853027</v>
@@ -2956,7 +2956,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>5.59882116317749</v>
+        <v>5.598821640014648</v>
       </c>
       <c r="C108" t="n">
         <v>6.943999767303467</v>
@@ -3014,7 +3014,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>4.956214427947998</v>
+        <v>4.956215381622314</v>
       </c>
       <c r="C110" t="n">
         <v>6.146999835968018</v>
@@ -3043,7 +3043,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>5.278873443603516</v>
+        <v>5.278873920440674</v>
       </c>
       <c r="C111" t="n">
         <v>6.495999813079834</v>
@@ -3101,7 +3101,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>4.778292179107666</v>
+        <v>4.778291702270508</v>
       </c>
       <c r="C113" t="n">
         <v>5.880000114440918</v>
@@ -3130,7 +3130,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>4.889699459075928</v>
+        <v>4.889700412750244</v>
       </c>
       <c r="C114" t="n">
         <v>5.966000080108643</v>
@@ -3159,7 +3159,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>4.606941699981689</v>
+        <v>4.606939792633057</v>
       </c>
       <c r="C115" t="n">
         <v>5.620999813079834</v>
@@ -3188,7 +3188,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>4.347947597503662</v>
+        <v>4.347949504852295</v>
       </c>
       <c r="C116" t="n">
         <v>5.304999828338623</v>
@@ -3217,7 +3217,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>4.147465705871582</v>
+        <v>4.147466659545898</v>
       </c>
       <c r="C117" t="n">
         <v>5.011000156402588</v>
@@ -3246,7 +3246,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>4.138363361358643</v>
+        <v>4.13836145401001</v>
       </c>
       <c r="C118" t="n">
         <v>5</v>
@@ -3275,7 +3275,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>5.555338859558105</v>
+        <v>5.555336475372314</v>
       </c>
       <c r="C119" t="n">
         <v>6.711999893188477</v>
@@ -3304,7 +3304,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>5.544636726379395</v>
+        <v>5.544635772705078</v>
       </c>
       <c r="C120" t="n">
         <v>6.646999835968018</v>
@@ -3333,7 +3333,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>5.784874439239502</v>
+        <v>5.784872531890869</v>
       </c>
       <c r="C121" t="n">
         <v>6.934999942779541</v>
@@ -3362,7 +3362,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>5.588011741638184</v>
+        <v>5.5880126953125</v>
       </c>
       <c r="C122" t="n">
         <v>6.698999881744385</v>
@@ -3391,7 +3391,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>5.696767807006836</v>
+        <v>5.696768283843994</v>
       </c>
       <c r="C123" t="n">
         <v>6.77400016784668</v>
@@ -3449,7 +3449,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>5.881781578063965</v>
+        <v>5.881781101226807</v>
       </c>
       <c r="C125" t="n">
         <v>6.99399995803833</v>
@@ -3478,7 +3478,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>6.179335117340088</v>
+        <v>6.179333686828613</v>
       </c>
       <c r="C126" t="n">
         <v>7.293000221252441</v>
@@ -3507,7 +3507,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>6.206446170806885</v>
+        <v>6.206447601318359</v>
       </c>
       <c r="C127" t="n">
         <v>7.324999809265137</v>
@@ -3536,7 +3536,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>6.414882659912109</v>
+        <v>6.414880752563477</v>
       </c>
       <c r="C128" t="n">
         <v>7.571000099182129</v>
@@ -3565,7 +3565,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>5.912634372711182</v>
+        <v>5.912631988525391</v>
       </c>
       <c r="C129" t="n">
         <v>6.926000118255615</v>
@@ -3594,7 +3594,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>5.9510498046875</v>
+        <v>5.951049327850342</v>
       </c>
       <c r="C130" t="n">
         <v>6.971000194549561</v>
@@ -3623,7 +3623,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>6.412039756774902</v>
+        <v>6.412040233612061</v>
       </c>
       <c r="C131" t="n">
         <v>7.511000156402588</v>
@@ -3652,7 +3652,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>6.864941596984863</v>
+        <v>6.864942073822021</v>
       </c>
       <c r="C132" t="n">
         <v>7.984000205993652</v>
@@ -3681,7 +3681,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>6.765199184417725</v>
+        <v>6.765199661254883</v>
       </c>
       <c r="C133" t="n">
         <v>7.868000030517578</v>
@@ -3710,7 +3710,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>7.318074226379395</v>
+        <v>7.318073272705078</v>
       </c>
       <c r="C134" t="n">
         <v>8.51099967956543</v>
@@ -3739,7 +3739,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>7.797452926635742</v>
+        <v>7.797454357147217</v>
       </c>
       <c r="C135" t="n">
         <v>9.01200008392334</v>
@@ -3768,7 +3768,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>8.225743293762207</v>
+        <v>8.225738525390625</v>
       </c>
       <c r="C136" t="n">
         <v>9.506999969482422</v>
@@ -3797,7 +3797,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>8.498290061950684</v>
+        <v>8.498287200927734</v>
       </c>
       <c r="C137" t="n">
         <v>9.821999549865723</v>
@@ -3826,7 +3826,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>9.046873092651367</v>
+        <v>9.046876907348633</v>
       </c>
       <c r="C138" t="n">
         <v>10.39999961853027</v>
@@ -3855,7 +3855,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>7.96038293838501</v>
+        <v>7.960382461547852</v>
       </c>
       <c r="C139" t="n">
         <v>9.151000022888184</v>
@@ -3884,7 +3884,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>8.057811737060547</v>
+        <v>8.057807922363281</v>
       </c>
       <c r="C140" t="n">
         <v>9.262999534606934</v>
@@ -3942,7 +3942,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>9.282994270324707</v>
+        <v>9.282997131347656</v>
       </c>
       <c r="C142" t="n">
         <v>10.60000038146973</v>
@@ -3971,7 +3971,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>9.536087036132812</v>
+        <v>9.536088943481445</v>
       </c>
       <c r="C143" t="n">
         <v>10.88899993896484</v>
@@ -4000,7 +4000,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>9.005839347839355</v>
+        <v>9.005838394165039</v>
       </c>
       <c r="C144" t="n">
         <v>10.22399997711182</v>
@@ -4029,7 +4029,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>9.255120277404785</v>
+        <v>9.255121231079102</v>
       </c>
       <c r="C145" t="n">
         <v>10.50699996948242</v>
@@ -4058,7 +4058,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>9.671764373779297</v>
+        <v>9.671765327453613</v>
       </c>
       <c r="C146" t="n">
         <v>10.97999954223633</v>
@@ -4087,7 +4087,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>10.03777503967285</v>
+        <v>10.03777408599854</v>
       </c>
       <c r="C147" t="n">
         <v>11.33100032806396</v>
@@ -4116,7 +4116,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>9.65684986114502</v>
+        <v>9.656848907470703</v>
       </c>
       <c r="C148" t="n">
         <v>10.90100002288818</v>
@@ -4145,7 +4145,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>9.012822151184082</v>
+        <v>9.012824058532715</v>
       </c>
       <c r="C149" t="n">
         <v>10.17399978637695</v>
@@ -4174,7 +4174,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>10.09888076782227</v>
+        <v>10.098876953125</v>
       </c>
       <c r="C150" t="n">
         <v>11.32299995422363</v>
@@ -4203,7 +4203,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>9.144553184509277</v>
+        <v>9.144556045532227</v>
       </c>
       <c r="C151" t="n">
         <v>10.25300025939941</v>
@@ -4232,7 +4232,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>10.47258186340332</v>
+        <v>10.47258377075195</v>
       </c>
       <c r="C152" t="n">
         <v>11.74199962615967</v>
@@ -4261,7 +4261,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>10.43202495574951</v>
+        <v>10.4320240020752</v>
       </c>
       <c r="C153" t="n">
         <v>11.62100028991699</v>
@@ -4290,7 +4290,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>9.130377769470215</v>
+        <v>9.130375862121582</v>
       </c>
       <c r="C154" t="n">
         <v>10.17099952697754</v>
@@ -4319,7 +4319,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>8.217429161071777</v>
+        <v>8.21743106842041</v>
       </c>
       <c r="C155" t="n">
         <v>9.154000282287598</v>
@@ -4377,7 +4377,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>8.099201202392578</v>
+        <v>8.099203109741211</v>
       </c>
       <c r="C157" t="n">
         <v>8.949000358581543</v>
@@ -4406,7 +4406,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>9.645008087158203</v>
+        <v>9.645007133483887</v>
       </c>
       <c r="C158" t="n">
         <v>10.6569995880127</v>
@@ -4435,7 +4435,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>10.52547931671143</v>
+        <v>10.52547645568848</v>
       </c>
       <c r="C159" t="n">
         <v>11.54899978637695</v>
@@ -4493,7 +4493,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>11.6182165145874</v>
+        <v>11.61821937561035</v>
       </c>
       <c r="C161" t="n">
         <v>12.7480001449585</v>
@@ -4551,7 +4551,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>10.8472146987915</v>
+        <v>10.84721565246582</v>
       </c>
       <c r="C163" t="n">
         <v>11.81999969482422</v>
@@ -4580,7 +4580,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>12.51008701324463</v>
+        <v>12.51008796691895</v>
       </c>
       <c r="C164" t="n">
         <v>13.63199996948242</v>
@@ -4609,7 +4609,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>13.6484842300415</v>
+        <v>13.64848709106445</v>
       </c>
       <c r="C165" t="n">
         <v>14.78999996185303</v>
@@ -4638,7 +4638,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>14.7143383026123</v>
+        <v>14.71433925628662</v>
       </c>
       <c r="C166" t="n">
         <v>15.94499969482422</v>
@@ -4667,7 +4667,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>15.59932994842529</v>
+        <v>15.59932422637939</v>
       </c>
       <c r="C167" t="n">
         <v>16.90399932861328</v>
@@ -4696,7 +4696,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>15.1944408416748</v>
+        <v>15.19443893432617</v>
       </c>
       <c r="C168" t="n">
         <v>16.38599967956543</v>
@@ -4725,7 +4725,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>16.52137565612793</v>
+        <v>16.52138137817383</v>
       </c>
       <c r="C169" t="n">
         <v>17.8169994354248</v>
@@ -4754,7 +4754,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>15.36876773834229</v>
+        <v>15.36876678466797</v>
       </c>
       <c r="C170" t="n">
         <v>16.57399940490723</v>
@@ -4783,7 +4783,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>14.32363033294678</v>
+        <v>14.32363224029541</v>
       </c>
       <c r="C171" t="n">
         <v>15.37100028991699</v>
@@ -4812,7 +4812,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>13.39456653594971</v>
+        <v>13.39456558227539</v>
       </c>
       <c r="C172" t="n">
         <v>14.37399959564209</v>
@@ -4841,7 +4841,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>15.2909049987793</v>
+        <v>15.29090118408203</v>
       </c>
       <c r="C173" t="n">
         <v>16.40900039672852</v>
@@ -4870,7 +4870,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>16.47625732421875</v>
+        <v>16.47625350952148</v>
       </c>
       <c r="C174" t="n">
         <v>17.59600067138672</v>
@@ -4899,7 +4899,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>18.21040344238281</v>
+        <v>18.21040153503418</v>
       </c>
       <c r="C175" t="n">
         <v>19.44799995422363</v>
@@ -4928,7 +4928,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>18.71135711669922</v>
+        <v>18.71135520935059</v>
       </c>
       <c r="C176" t="n">
         <v>19.98299980163574</v>
@@ -4957,7 +4957,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>19.29125595092773</v>
+        <v>19.29125785827637</v>
       </c>
       <c r="C177" t="n">
         <v>20.51399993896484</v>
@@ -4986,7 +4986,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>18.21921157836914</v>
+        <v>18.21920776367188</v>
       </c>
       <c r="C178" t="n">
         <v>19.37400054931641</v>
@@ -5044,7 +5044,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>23.78690719604492</v>
+        <v>23.78691101074219</v>
       </c>
       <c r="C180" t="n">
         <v>25.19700050354004</v>
@@ -5073,7 +5073,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>24.44206428527832</v>
+        <v>24.44206809997559</v>
       </c>
       <c r="C181" t="n">
         <v>25.89100074768066</v>
@@ -5102,7 +5102,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>26.43964958190918</v>
+        <v>26.43964767456055</v>
       </c>
       <c r="C182" t="n">
         <v>28.00699996948242</v>
@@ -5131,7 +5131,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>29.4615421295166</v>
+        <v>29.46154403686523</v>
       </c>
       <c r="C183" t="n">
         <v>31.12299919128418</v>
@@ -5189,7 +5189,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>29.85154914855957</v>
+        <v>29.85154724121094</v>
       </c>
       <c r="C185" t="n">
         <v>31.53499984741211</v>
@@ -5218,7 +5218,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>30.08857917785645</v>
+        <v>30.08857727050781</v>
       </c>
       <c r="C186" t="n">
         <v>31.68899917602539</v>
@@ -5247,7 +5247,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>30.78361320495605</v>
+        <v>30.78361511230469</v>
       </c>
       <c r="C187" t="n">
         <v>32.42100143432617</v>
@@ -5276,7 +5276,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>33.05765914916992</v>
+        <v>33.05766296386719</v>
       </c>
       <c r="C188" t="n">
         <v>34.81600189208984</v>
@@ -5305,7 +5305,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>32.38256454467773</v>
+        <v>32.38257598876953</v>
       </c>
       <c r="C189" t="n">
         <v>33.99599838256836</v>
@@ -5334,7 +5334,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>31.86343193054199</v>
+        <v>31.86344337463379</v>
       </c>
       <c r="C190" t="n">
         <v>33.45100021362305</v>
@@ -5363,7 +5363,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>35.50691223144531</v>
+        <v>35.50690460205078</v>
       </c>
       <c r="C191" t="n">
         <v>37.2760009765625</v>
@@ -5392,7 +5392,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>38.97518157958984</v>
+        <v>38.97518539428711</v>
       </c>
       <c r="C192" t="n">
         <v>40.8129997253418</v>
@@ -5421,7 +5421,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>41.07420349121094</v>
+        <v>41.0742073059082</v>
       </c>
       <c r="C193" t="n">
         <v>43.01100158691406</v>
@@ -5450,7 +5450,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>37.17411041259766</v>
+        <v>37.17410659790039</v>
       </c>
       <c r="C194" t="n">
         <v>38.92699813842773</v>
@@ -5479,7 +5479,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>33.37059783935547</v>
+        <v>33.37060165405273</v>
       </c>
       <c r="C195" t="n">
         <v>34.84999847412109</v>
@@ -5508,7 +5508,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>35.05205535888672</v>
+        <v>35.05206680297852</v>
       </c>
       <c r="C196" t="n">
         <v>36.60599899291992</v>
@@ -5537,7 +5537,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>30.57073211669922</v>
+        <v>30.57073020935059</v>
       </c>
       <c r="C197" t="n">
         <v>31.92600059509277</v>
@@ -5566,7 +5566,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>35.05282592773438</v>
+        <v>35.05282211303711</v>
       </c>
       <c r="C198" t="n">
         <v>36.48500061035156</v>
@@ -5624,7 +5624,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>36.84845733642578</v>
+        <v>36.84845352172852</v>
       </c>
       <c r="C200" t="n">
         <v>38.35400009155273</v>
@@ -5653,7 +5653,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>33.17786407470703</v>
+        <v>33.1778678894043</v>
       </c>
       <c r="C201" t="n">
         <v>34.41299819946289</v>
@@ -5682,7 +5682,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>29.17681312561035</v>
+        <v>29.17681694030762</v>
       </c>
       <c r="C202" t="n">
         <v>30.26300048828125</v>
@@ -5711,7 +5711,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>30.50921440124512</v>
+        <v>30.50921249389648</v>
       </c>
       <c r="C203" t="n">
         <v>31.64500045776367</v>
@@ -5740,7 +5740,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>38.03396606445312</v>
+        <v>38.03396987915039</v>
       </c>
       <c r="C204" t="n">
         <v>39.31499862670898</v>
@@ -5798,7 +5798,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>37.96915817260742</v>
+        <v>37.96916198730469</v>
       </c>
       <c r="C206" t="n">
         <v>39.24800109863281</v>
@@ -5885,7 +5885,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>37.51530456542969</v>
+        <v>37.51529693603516</v>
       </c>
       <c r="C209" t="n">
         <v>38.65399932861328</v>
@@ -5914,7 +5914,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>43.13909149169922</v>
+        <v>43.13909912109375</v>
       </c>
       <c r="C210" t="n">
         <v>44.29899978637695</v>
@@ -5943,7 +5943,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>47.23205184936523</v>
+        <v>47.2320442199707</v>
       </c>
       <c r="C211" t="n">
         <v>48.50199890136719</v>
@@ -5972,7 +5972,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>50.04929351806641</v>
+        <v>50.04930114746094</v>
       </c>
       <c r="C212" t="n">
         <v>51.39500045776367</v>
@@ -6001,7 +6001,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>49.00592803955078</v>
+        <v>49.00593185424805</v>
       </c>
       <c r="C213" t="n">
         <v>50.1870002746582</v>
@@ -6059,7 +6059,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>45.86465072631836</v>
+        <v>45.86464309692383</v>
       </c>
       <c r="C215" t="n">
         <v>46.97000122070312</v>
@@ -6088,7 +6088,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>53.32671356201172</v>
+        <v>53.32670974731445</v>
       </c>
       <c r="C216" t="n">
         <v>54.46200180053711</v>
@@ -6204,7 +6204,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>68.55281066894531</v>
+        <v>68.55281829833984</v>
       </c>
       <c r="C220" t="n">
         <v>69.85700225830078</v>
@@ -6233,7 +6233,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>67.64213562011719</v>
+        <v>67.64215087890625</v>
       </c>
       <c r="C221" t="n">
         <v>68.92900085449219</v>
@@ -6291,7 +6291,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>81.07630157470703</v>
+        <v>81.07630920410156</v>
       </c>
       <c r="C223" t="n">
         <v>82.45099639892578</v>
@@ -6320,7 +6320,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>80.93470001220703</v>
+        <v>80.93470764160156</v>
       </c>
       <c r="C224" t="n">
         <v>82.30699920654297</v>
@@ -6349,7 +6349,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>80.72422027587891</v>
+        <v>80.72421264648438</v>
       </c>
       <c r="C225" t="n">
         <v>81.94300079345703</v>
@@ -6436,7 +6436,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>63.9174690246582</v>
+        <v>63.91748046875</v>
       </c>
       <c r="C228" t="n">
         <v>64.7030029296875</v>
@@ -6465,7 +6465,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>62.24700164794922</v>
+        <v>62.24700546264648</v>
       </c>
       <c r="C229" t="n">
         <v>63.01200103759766</v>
@@ -6494,7 +6494,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>72.92774200439453</v>
+        <v>72.927734375</v>
       </c>
       <c r="C230" t="n">
         <v>73.82399749755859</v>
@@ -6552,7 +6552,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>67.30638885498047</v>
+        <v>67.306396484375</v>
       </c>
       <c r="C232" t="n">
         <v>67.98000335693359</v>
@@ -6610,7 +6610,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>75.11841583251953</v>
+        <v>75.118408203125</v>
       </c>
       <c r="C234" t="n">
         <v>75.68800354003906</v>
@@ -6697,7 +6697,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>86.73211669921875</v>
+        <v>86.73210906982422</v>
       </c>
       <c r="C237" t="n">
         <v>87.19999694824219</v>
@@ -6726,7 +6726,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>107.2812652587891</v>
+        <v>107.28125</v>
       </c>
       <c r="C238" t="n">
         <v>107.8600006103516</v>
@@ -6755,7 +6755,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>120.2254333496094</v>
+        <v>120.2254257202148</v>
       </c>
       <c r="C239" t="n">
         <v>120.8740005493164</v>
@@ -6784,7 +6784,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>117.1124420166016</v>
+        <v>117.1124496459961</v>
       </c>
       <c r="C240" t="n">
         <v>117.5469970703125</v>
@@ -6842,7 +6842,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>142.26611328125</v>
+        <v>142.2661285400391</v>
       </c>
       <c r="C242" t="n">
         <v>142.7940063476562</v>
@@ -6929,7 +6929,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>174.6145324707031</v>
+        <v>174.6145172119141</v>
       </c>
       <c r="C245" t="n">
         <v>175.0350036621094</v>
